--- a/extras/bio/生物DSE_卷一MC_答案與得分率_2012-2022.xlsx
+++ b/extras/bio/生物DSE_卷一MC_答案與得分率_2012-2022.xlsx
@@ -39,7 +39,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -64,6 +64,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F8CBAD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -93,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -111,6 +116,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -478,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -771,6 +779,66 @@
         <v>62</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -782,7 +850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D397"/>
+  <dimension ref="A1:D469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7145,6 +7213,1446 @@
       </c>
       <c r="D397" s="2" t="n">
         <v>63</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="7" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B398" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C398" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D398" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="7" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B399" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C399" s="7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D399" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="7" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B400" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C400" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D400" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="7" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B401" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C401" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D401" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="7" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B402" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C402" s="7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D402" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="7" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B403" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C403" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D403" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="7" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B404" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C404" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D404" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="7" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B405" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C405" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D405" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="7" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B406" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C406" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D406" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="7" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B407" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C407" s="7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D407" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="7" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B408" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C408" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D408" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="7" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B409" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="C409" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D409" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="7" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B410" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="C410" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D410" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="7" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B411" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C411" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D411" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="7" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B412" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="C412" s="7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D412" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="7" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B413" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="C413" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D413" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="7" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B414" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="C414" s="7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D414" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="7" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B415" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="C415" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D415" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="7" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B416" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="C416" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D416" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="7" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B417" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="C417" s="7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D417" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="7" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B418" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="C418" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D418" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="7" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B419" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="C419" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D419" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="7" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B420" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="C420" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D420" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="7" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B421" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="C421" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D421" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="7" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B422" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="C422" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D422" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="7" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B423" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="C423" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D423" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="7" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B424" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="C424" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D424" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="7" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B425" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="C425" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D425" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="7" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B426" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="C426" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D426" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="7" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B427" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="C427" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D427" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="7" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B428" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="C428" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D428" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="7" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B429" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="C429" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D429" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="7" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B430" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="C430" s="7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D430" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="7" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B431" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="C431" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D431" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="7" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B432" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="C432" s="7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D432" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="7" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B433" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="C433" s="7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D433" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B434" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C434" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D434" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B435" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C435" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D435" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B436" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C436" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D436" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B437" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C437" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D437" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B438" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C438" s="7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D438" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B439" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C439" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D439" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B440" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C440" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D440" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B441" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C441" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D441" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B442" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C442" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D442" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B443" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C443" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D443" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B444" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C444" s="7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D444" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B445" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="C445" s="7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D445" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B446" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="C446" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D446" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B447" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C447" s="7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D447" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B448" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="C448" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D448" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B449" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="C449" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D449" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B450" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="C450" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D450" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B451" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="C451" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D451" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B452" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="C452" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D452" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B453" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="C453" s="7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D453" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B454" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="C454" s="7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D454" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B455" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="C455" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D455" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B456" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="C456" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D456" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B457" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="C457" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D457" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B458" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="C458" s="7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D458" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B459" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="C459" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D459" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B460" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="C460" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D460" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B461" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="C461" s="7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D461" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B462" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="C462" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D462" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B463" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="C463" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D463" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B464" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="C464" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D464" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B465" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="C465" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D465" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B466" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="C466" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D466" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B467" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="C467" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D467" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B468" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="C468" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D468" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B469" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="C469" s="7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D469" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -7159,7 +8667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -7237,2164 +8745,2534 @@
           <t>2022</t>
         </is>
       </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>D 73%</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>D 54%</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>D 64%</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>D 49%</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>C 85%</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>C 67%</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>D 71%</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>B 83%</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>A 63%</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>D 60%</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" s="7" t="inlineStr">
         <is>
           <t>A 56%</t>
         </is>
       </c>
+      <c r="M2" s="7" t="inlineStr">
+        <is>
+          <t>C —</t>
+        </is>
+      </c>
+      <c r="N2" s="7" t="inlineStr">
+        <is>
+          <t>C —</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>D 33%</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>C 76%</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>C 32%</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>A 78%</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>B 69%</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>B 67%</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>C 54%</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>D 44%</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>C 85%</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="7" t="inlineStr">
         <is>
           <t>D 63%</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="7" t="inlineStr">
         <is>
           <t>C 60%</t>
         </is>
       </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>D —</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="inlineStr">
+        <is>
+          <t>B —</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>A 68%</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>C 72%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>D 59%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>B 60%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>D 43%</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>A 34%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>B 76%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>B 61%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>C 71%</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" s="7" t="inlineStr">
         <is>
           <t>C 57%</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L4" s="7" t="inlineStr">
         <is>
           <t>A 35%</t>
         </is>
       </c>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>A —</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="inlineStr">
+        <is>
+          <t>A —</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>B 63%</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>A 81%</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>D 41%</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>D 57%</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>B 33%</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>C 23%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>A 69%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>B 49%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>A 64%</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>D 85%</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>B 66%</t>
         </is>
       </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>B —</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>C —</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>D 61%</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>C 41%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>B 41%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>C 74%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>A 52%</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>A 60%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>D 37%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>D 45%</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>B 73%</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" s="7" t="inlineStr">
         <is>
           <t>B 42%</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L6" s="7" t="inlineStr">
         <is>
           <t>B 44%</t>
         </is>
       </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>D —</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>D —</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>A 79%</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>A 47%</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>A 70%</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>B 53%</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>A 68%</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>C 73%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>D 89%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>A 77%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>B 70%</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" s="7" t="inlineStr">
         <is>
           <t>A 62%</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="L7" s="7" t="inlineStr">
         <is>
           <t>D 51%</t>
         </is>
       </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>B —</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>A —</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>A 76%</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>B 44%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>A 74%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>D 47%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>A 80%</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>C 58%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>A 74%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>C 31%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>D 41%</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K8" s="7" t="inlineStr">
         <is>
           <t>C 65%</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="L8" s="7" t="inlineStr">
         <is>
           <t>C 64%</t>
         </is>
       </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>C —</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>B —</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>A 81%</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>C 42%</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>B 47%</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>A 76%</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>C 64%</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>B 79%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>C 63%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>A 73%</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>D 78%</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="7" t="inlineStr">
         <is>
           <t>B 38%</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L9" s="7" t="inlineStr">
         <is>
           <t>D 62%</t>
         </is>
       </c>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>A —</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>C —</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>D 87%</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>B 70%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>B 36%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>A 79%</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>A 53%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>C 41%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>B 72%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>D 45%</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K10" s="7" t="inlineStr">
         <is>
           <t>A 57%</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="L10" s="7" t="inlineStr">
         <is>
           <t>C 73%</t>
         </is>
       </c>
+      <c r="M10" s="7" t="inlineStr">
+        <is>
+          <t>A —</t>
+        </is>
+      </c>
+      <c r="N10" s="7" t="inlineStr">
+        <is>
+          <t>C —</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>C 69%</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>D 67%</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>A 50%</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>C 43%</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>C 67%</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>D 58%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>A 78%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>A 22%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>B 86%</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K11" s="7" t="inlineStr">
         <is>
           <t>B 52%</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L11" s="7" t="inlineStr">
         <is>
           <t>D 80%</t>
         </is>
       </c>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>D —</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="inlineStr">
+        <is>
+          <t>C —</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>A 64%</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>C 35%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>A 31%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>B 96%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>D 73%</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>D 81%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>D 69%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>B 23%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>C 80%</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K12" s="7" t="inlineStr">
         <is>
           <t>C 63%</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L12" s="7" t="inlineStr">
         <is>
           <t>B 51%</t>
         </is>
       </c>
+      <c r="M12" s="7" t="inlineStr">
+        <is>
+          <t>B —</t>
+        </is>
+      </c>
+      <c r="N12" s="7" t="inlineStr">
+        <is>
+          <t>D —</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>D 48%</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>C 80%</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>B 80%</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>D 60%</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>A 69%</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>B 71%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>A 39%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>D 87%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>D 59%</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K13" s="7" t="inlineStr">
         <is>
           <t>C 58%</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="L13" s="7" t="inlineStr">
         <is>
           <t>B 74%</t>
         </is>
       </c>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>A —</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr">
+        <is>
+          <t>D —</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>B 54%</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>B 84%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>C 83%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>B 73%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>B 47%</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>A 57%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>C 77%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>D 45%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>A 82%</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K14" s="7" t="inlineStr">
         <is>
           <t>A 53%</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="L14" s="7" t="inlineStr">
         <is>
           <t>B 69%</t>
         </is>
       </c>
+      <c r="M14" s="7" t="inlineStr">
+        <is>
+          <t>A —</t>
+        </is>
+      </c>
+      <c r="N14" s="7" t="inlineStr">
+        <is>
+          <t>A —</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>A 61%</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>A 80%</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>A 45%</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>A 67%</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>B 68%</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>B 53%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>A 91%</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>D 63%</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>B 53%</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K15" s="7" t="inlineStr">
         <is>
           <t>A 73%</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="L15" s="7" t="inlineStr">
         <is>
           <t>A 55%</t>
         </is>
       </c>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>B —</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="inlineStr">
+        <is>
+          <t>D —</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>B 63%</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>B 47%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>D 35%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>A 76%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>B 51%</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>A 76%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>D 61%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>A 35%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>B 91%</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K16" s="7" t="inlineStr">
         <is>
           <t>D 75%</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="L16" s="7" t="inlineStr">
         <is>
           <t>D 70%</t>
         </is>
       </c>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>D —</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="inlineStr">
+        <is>
+          <t>B —</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>C 78%</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>D 55%</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>A 71%</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>C 88%</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>C 76%</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>D 61%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>D 51%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>D 56%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>A 56%</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K17" s="7" t="inlineStr">
         <is>
           <t>D 40%</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="L17" s="7" t="inlineStr">
         <is>
           <t>B 48%</t>
         </is>
       </c>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>C —</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="inlineStr">
+        <is>
+          <t>A —</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>C 80%</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>B 71%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>B 81%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>B 75%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>C 40%</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t>C 51%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>C 59%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>C 59%</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>D 58%</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="K18" s="7" t="inlineStr">
         <is>
           <t>C 38%</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="L18" s="7" t="inlineStr">
         <is>
           <t>C 69%</t>
         </is>
       </c>
+      <c r="M18" s="7" t="inlineStr">
+        <is>
+          <t>D —</t>
+        </is>
+      </c>
+      <c r="N18" s="7" t="inlineStr">
+        <is>
+          <t>B —</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>D 78%</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>D 32%</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>A 31%</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>A 78%</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>D 67%</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>D 49%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>C 63%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>A 61%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>C 74%</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="K19" s="7" t="inlineStr">
         <is>
           <t>A 68%</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="L19" s="7" t="inlineStr">
         <is>
           <t>A 61%</t>
         </is>
       </c>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>B —</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>A —</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>A 31%</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>B 59%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>C 14%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>D 40%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>C 34%</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="7" t="inlineStr">
         <is>
           <t>B 78%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>B 73%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>D 84%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>A 52%</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="K20" s="7" t="inlineStr">
         <is>
           <t>C 73%</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="L20" s="7" t="inlineStr">
         <is>
           <t>D 51%</t>
         </is>
       </c>
+      <c r="M20" s="7" t="inlineStr">
+        <is>
+          <t>C —</t>
+        </is>
+      </c>
+      <c r="N20" s="7" t="inlineStr">
+        <is>
+          <t>C —</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>B 64%</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>A 78%</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>D 78%</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>C 67%</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>D 59%</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" s="7" t="inlineStr">
         <is>
           <t>B 76%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>D 50%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>B 65%</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>A 34%</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="K21" s="7" t="inlineStr">
         <is>
           <t>D 70%</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="L21" s="7" t="inlineStr">
         <is>
           <t>B 46%</t>
         </is>
       </c>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>D —</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr">
+        <is>
+          <t>D —</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>D 83%</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>D 54%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>D 65%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>D 39%</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>D 71%</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>B 53%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>C 58%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>D 54%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>A 66%</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="K22" s="7" t="inlineStr">
         <is>
           <t>C 71%</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="L22" s="7" t="inlineStr">
         <is>
           <t>D 47%</t>
         </is>
       </c>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>C —</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="inlineStr">
+        <is>
+          <t>D —</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>C 82%</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>A 60%</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>C 73%</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>A 86%</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>C 85%</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>C 63%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>A 76%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I23" s="7" t="inlineStr">
         <is>
           <t>D 39%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>C 28%</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="K23" s="7" t="inlineStr">
         <is>
           <t>D 67%</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="L23" s="7" t="inlineStr">
         <is>
           <t>D 27%</t>
         </is>
       </c>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>C —</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr">
+        <is>
+          <t>B —</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>B 68%</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>D 48%</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>A 61%</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>C 84%</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>A 73%</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="7" t="inlineStr">
         <is>
           <t>D 49%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>B 74%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>C 45%</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>B 64%</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="K24" s="7" t="inlineStr">
         <is>
           <t>B 48%</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="L24" s="7" t="inlineStr">
         <is>
           <t>B 51%</t>
         </is>
       </c>
+      <c r="M24" s="7" t="inlineStr">
+        <is>
+          <t>B —</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="inlineStr">
+        <is>
+          <t>A —</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>C 37%</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>A 65%</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>A 63%</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>D 78%</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" s="7" t="inlineStr">
         <is>
           <t>C 36%</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>C 87%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>B 51%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>C 41%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>B 63%</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="K25" s="7" t="inlineStr">
         <is>
           <t>D 66%</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="L25" s="7" t="inlineStr">
         <is>
           <t>A 52%</t>
         </is>
       </c>
+      <c r="M25" s="7" t="inlineStr">
+        <is>
+          <t>C —</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="inlineStr">
+        <is>
+          <t>B —</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>C 93%</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>B 24%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>B 47%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>C 64%</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>D 58%</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>A 79%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H26" s="7" t="inlineStr">
         <is>
           <t>D 36%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>C 68%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J26" s="7" t="inlineStr">
         <is>
           <t>A 57%</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="K26" s="7" t="inlineStr">
         <is>
           <t>D 65%</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="L26" s="7" t="inlineStr">
         <is>
           <t>C 56%</t>
         </is>
       </c>
+      <c r="M26" s="7" t="inlineStr">
+        <is>
+          <t>A —</t>
+        </is>
+      </c>
+      <c r="N26" s="7" t="inlineStr">
+        <is>
+          <t>D —</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>B 82%</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>B 33%</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>A 62%</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>A 42%</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>A 65%</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" s="7" t="inlineStr">
         <is>
           <t>D 73%</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>A 50%</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>A 80%</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>D 49%</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="K27" s="7" t="inlineStr">
         <is>
           <t>B 35%</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="L27" s="7" t="inlineStr">
         <is>
           <t>C 44%</t>
         </is>
       </c>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>A —</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="inlineStr">
+        <is>
+          <t>B —</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>C 79%</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>B 64%</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>B 62%</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>C 72%</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr">
         <is>
           <t>B 18%</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" s="7" t="inlineStr">
         <is>
           <t>C 71%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H28" s="7" t="inlineStr">
         <is>
           <t>B 96%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>C 50%</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J28" s="7" t="inlineStr">
         <is>
           <t>C 61%</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="K28" s="7" t="inlineStr">
         <is>
           <t>B 75%</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="L28" s="7" t="inlineStr">
         <is>
           <t>D 62%</t>
         </is>
       </c>
+      <c r="M28" s="7" t="inlineStr">
+        <is>
+          <t>C —</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="inlineStr">
+        <is>
+          <t>A —</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>B 58%</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>A 55%</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>C 53%</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>A 59%</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>C 18%</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" s="7" t="inlineStr">
         <is>
           <t>A 66%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>A 63%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>B 45%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>B 84%</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="K29" s="7" t="inlineStr">
         <is>
           <t>A 12%</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="L29" s="7" t="inlineStr">
         <is>
           <t>A 85%</t>
         </is>
       </c>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>A —</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="inlineStr">
+        <is>
+          <t>D —</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>B 46%</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>C 62%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>C 78%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>D 91%</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>B 73%</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>C 53%</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>D 28%</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>A 68%</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J30" s="7" t="inlineStr">
         <is>
           <t>C 70%</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="K30" s="7" t="inlineStr">
         <is>
           <t>C 60%</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="L30" s="7" t="inlineStr">
         <is>
           <t>A 61%</t>
         </is>
       </c>
+      <c r="M30" s="7" t="inlineStr">
+        <is>
+          <t>B —</t>
+        </is>
+      </c>
+      <c r="N30" s="7" t="inlineStr">
+        <is>
+          <t>C —</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>C 35%</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>C 7%</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>D 69%</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>C 79%</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F31" s="7" t="inlineStr">
         <is>
           <t>A 61%</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>D 87%</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H31" s="7" t="inlineStr">
         <is>
           <t>B 76%</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>C 18%</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="J31" s="7" t="inlineStr">
         <is>
           <t>C 65%</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="K31" s="7" t="inlineStr">
         <is>
           <t>B 44%</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="L31" s="7" t="inlineStr">
         <is>
           <t>C 91%</t>
         </is>
       </c>
+      <c r="M31" s="7" t="inlineStr">
+        <is>
+          <t>B —</t>
+        </is>
+      </c>
+      <c r="N31" s="7" t="inlineStr">
+        <is>
+          <t>C —</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>A 90%</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>B 64%</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>D 51%</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>B 58%</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>D 70%</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G32" s="7" t="inlineStr">
         <is>
           <t>D 65%</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H32" s="7" t="inlineStr">
         <is>
           <t>B 81%</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I32" s="7" t="inlineStr">
         <is>
           <t>C 45%</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J32" s="7" t="inlineStr">
         <is>
           <t>D 81%</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="K32" s="7" t="inlineStr">
         <is>
           <t>B 30%</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="L32" s="7" t="inlineStr">
         <is>
           <t>D 33%</t>
         </is>
       </c>
+      <c r="M32" s="7" t="inlineStr">
+        <is>
+          <t>B —</t>
+        </is>
+      </c>
+      <c r="N32" s="7" t="inlineStr">
+        <is>
+          <t>B —</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>D 75%</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>B 47%</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>C 61%</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>A 38%</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr">
         <is>
           <t>B 30%</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" s="7" t="inlineStr">
         <is>
           <t>D 56%</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H33" s="7" t="inlineStr">
         <is>
           <t>C 64%</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="I33" s="7" t="inlineStr">
         <is>
           <t>D 50%</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="J33" s="7" t="inlineStr">
         <is>
           <t>B 92%</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
+      <c r="K33" s="7" t="inlineStr">
         <is>
           <t>A 54%</t>
         </is>
       </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="L33" s="7" t="inlineStr">
         <is>
           <t>D 64%</t>
         </is>
       </c>
+      <c r="M33" s="7" t="inlineStr">
+        <is>
+          <t>A —</t>
+        </is>
+      </c>
+      <c r="N33" s="7" t="inlineStr">
+        <is>
+          <t>C —</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>C 76%</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>A 79%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>B 45%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>C 80%</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F34" s="7" t="inlineStr">
         <is>
           <t>B 46%</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" s="7" t="inlineStr">
         <is>
           <t>C 62%</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H34" s="7" t="inlineStr">
         <is>
           <t>B 77%</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I34" s="7" t="inlineStr">
         <is>
           <t>B 70%</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="J34" s="7" t="inlineStr">
         <is>
           <t>D 43%</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="K34" s="7" t="inlineStr">
         <is>
           <t>B 80%</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="L34" s="7" t="inlineStr">
         <is>
           <t>C 33%</t>
         </is>
       </c>
+      <c r="M34" s="7" t="inlineStr">
+        <is>
+          <t>D —</t>
+        </is>
+      </c>
+      <c r="N34" s="7" t="inlineStr">
+        <is>
+          <t>C —</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>C 74%</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>C 81%</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>D 54%</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>D 47%</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>D 47%</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G35" s="7" t="inlineStr">
         <is>
           <t>B 62%</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H35" s="7" t="inlineStr">
         <is>
           <t>A 38%</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="I35" s="7" t="inlineStr">
         <is>
           <t>C 81%</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="J35" s="7" t="inlineStr">
         <is>
           <t>D 57%</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="K35" s="7" t="inlineStr">
         <is>
           <t>C 61%</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="L35" s="7" t="inlineStr">
         <is>
           <t>C 63%</t>
         </is>
       </c>
+      <c r="M35" s="7" t="inlineStr">
+        <is>
+          <t>C —</t>
+        </is>
+      </c>
+      <c r="N35" s="7" t="inlineStr">
+        <is>
+          <t>B —</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>B 71%</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>D 90%</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>B 58%</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>B 81%</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>A 42%</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G36" s="7" t="inlineStr">
         <is>
           <t>A 56%</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>D 20%</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>A 48%</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="J36" s="7" t="inlineStr">
         <is>
           <t>A 38%</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="K36" s="7" t="inlineStr">
         <is>
           <t>A 47%</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="L36" s="7" t="inlineStr">
         <is>
           <t>B 59%</t>
         </is>
       </c>
+      <c r="M36" s="7" t="inlineStr">
+        <is>
+          <t>D —</t>
+        </is>
+      </c>
+      <c r="N36" s="7" t="inlineStr">
+        <is>
+          <t>A —</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>B 70%</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>D 55%</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>C 77%</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>D 34%</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>D 64%</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G37" s="7" t="inlineStr">
         <is>
           <t>A 78%</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H37" s="7" t="inlineStr">
         <is>
           <t>C 66%</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="I37" s="7" t="inlineStr">
         <is>
           <t>C 66%</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="J37" s="7" t="inlineStr">
         <is>
           <t>C 41%</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="K37" s="7" t="inlineStr">
         <is>
           <t>C 54%</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="L37" s="7" t="inlineStr">
         <is>
           <t>A 63%</t>
+        </is>
+      </c>
+      <c r="M37" s="7" t="inlineStr">
+        <is>
+          <t>D —</t>
+        </is>
+      </c>
+      <c r="N37" s="7" t="inlineStr">
+        <is>
+          <t>D —</t>
         </is>
       </c>
     </row>
@@ -10027,7 +11905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10251,6 +12129,44 @@
         <v>10</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
